--- a/templates/07_周报月报模板.xlsx
+++ b/templates/07_周报月报模板.xlsx
@@ -1280,7 +1280,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>杭州滨江云璟酒店 · 320 间房 · 中高端全服务 ｜ 酒店收益管理学院 HRMA ｜ 口径以 SPEC.md 为准</t>
+          <t>杭州滨江云璟酒店 · 320 间房 · 中高端全服务 ｜ RMC收益管理社区 ｜ 口径以 SPEC.md 为准</t>
         </is>
       </c>
     </row>
